--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\may04\PycharmProjects\SimpleTrader\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E2605A-1A8C-4B01-A117-C2EA5D9D931D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFB5AE5-EB0D-43B1-B2E6-8202D13658CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,9 +36,6 @@
     <t>class_code</t>
   </si>
   <si>
-    <t>TQCB</t>
-  </si>
-  <si>
     <t>ОФЗ 26238</t>
   </si>
   <si>
@@ -67,6 +64,9 @@
   </si>
   <si>
     <t>SU26245RMFS9</t>
+  </si>
+  <si>
+    <t>TQOB</t>
   </si>
 </sst>
 </file>
@@ -405,57 +405,57 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
